--- a/光伏配储项目/电价数据/2026/义和站.xlsx
+++ b/光伏配储项目/电价数据/2026/义和站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5318999999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59846</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59072</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5297500000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42713</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5007200000000001</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11803</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13674</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06775</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10851</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16238</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.6642100000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.02561</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14716</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22898</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23458</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21815</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.59361</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.13768</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14448</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53853</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.63527</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73203</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0547</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.7658400000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6587999999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.79552</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.13135</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.27079</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.96936</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.21278</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40153</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6148899999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.66783</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.39089</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.11723</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86949</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79671</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7574099999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51889</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47973</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42548</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70943</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76631</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87087</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9154800000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48561</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8862300000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7240800000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.82168</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45758</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50904</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77342</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9886699999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5214500000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89795</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8517899999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7136699999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.19611</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08008</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.04078</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49573</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52612</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85951</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.63142</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7528899999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7382799999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.12166</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.9295599999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8283400000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.16696</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.06873</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.22382</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.00308</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.0538</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6093500000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9466100000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90262</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.96475</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.93611</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.76293</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.67431</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80663</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33463</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50831</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48873</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.49614</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23182</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.54928</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48967</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81997</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.58694</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7248300000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81345</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.51352</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.86674</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.66242</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60065</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.43801</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.56057</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50607</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5699099999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5946900000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5425099999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56226</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27019</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61726</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.58617</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50396</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53486</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.55698</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58765</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45712</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48517</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6137100000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.63164</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56202</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.75601</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.63444</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.54918</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.46476</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5993200000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5275599999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49369</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41537</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.25511</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.23293</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6236699999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.6265499999999999</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46076</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.20462</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.53295</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6070800000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49642</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48901</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49924</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.56971</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55471</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32115</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.17816</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22338</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20037</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15674</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.21482</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.02014</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.17516</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.14094</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.17109</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.01449</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00329</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.50315</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35194</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6655399999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22383</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.00076</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07798000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07623999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33599</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31739</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45643</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8680800000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33087</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.51971</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39991</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20702</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59739</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5849500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88312</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63591</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86251</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.70674</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7079099999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60087</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35433</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9195599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46825</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16198</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19903</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.60564</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47328</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16188</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70145</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79232</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59154</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45561</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55649</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16158</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57472</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.85217</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.46582</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32594</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22553</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13323</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13232</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13843</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13326</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24496</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13198</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11358</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09340999999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10967</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19198</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13127</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35046</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5446599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23564</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.47697</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.5425399999999999</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24286</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42214</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36171</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.2176</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.68537</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45356</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.32982</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.15074</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.7851900000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.23989</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.37471</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.57247</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.78164</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.58097</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.61326</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.75904</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.04557</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.62899</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69431</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.69262</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.58061</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34815</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40328</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3505</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65749</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.79589</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3459</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.20918</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.21178</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.21994</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20172</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.12758</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22523</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23197</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.20959</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.15474</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.26174</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.26905</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.12923</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.21428</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>-0.01273</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.22958</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.56928</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7522300000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.06906999999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.16417</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.13957</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35063</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5330900000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6246799999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5093299999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46138</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.52804</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.56456</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5215599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.64427</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64824</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.5501900000000001</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.97336</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47482</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50806</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62762</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73765</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7192499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.48752</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.74012</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76523</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61809</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66671</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44009</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50913</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.07201</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44401</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15036</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21575</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33551</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25909</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25508</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18901</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26097</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09741</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19262</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.21254</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24832</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23984</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32652</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21716</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04821</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02911</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00057</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03863</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01781</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20147</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26403</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34693</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.84311</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.7083700000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5470700000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.45891</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9865499999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87946</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83989</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10047</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.15871</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.21454</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.18587</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.20103</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03114</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.15428</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.01683</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17051</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01449</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.18348</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.02421</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17696</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.19588</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.72292</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.8606200000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.86799</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.86482</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.48647</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9868899999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.8653500000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.89249</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.89109</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84627</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8444400000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84881</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9457899999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.86085</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8869900000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.86134</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.37996</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5048899999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6881499999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8759400000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.6451699999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49981</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.54706</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52966</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.25217</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.25669</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.66335</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.54714</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1.72376</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>1.74465</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26215</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.73337</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43279</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.5057699999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8914500000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6958799999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46172</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.44595</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.45479</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.6545700000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.84051</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.6369199999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.25061</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.11732</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42509</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.07499</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.25967</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81713</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5174299999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.43669</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82697</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7919700000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.50912</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.50976</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.44577</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36951</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47965</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.6635800000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.73898</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.82125</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.0144</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.23974</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.18236</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.04671</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.56746</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.82914</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.36478</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.16932</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.07374</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.85417</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37381</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.20875</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.19105</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25813</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.10635</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14464</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16606</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.15038</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18852</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.11012</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.20717</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.22555</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46817</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38145</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.04185</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.96224</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.61446</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43807</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.6548200000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.77318</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.75993</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.90408</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.72465</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.12246</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.634</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.5665</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8649199999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5714199999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.69021</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.64967</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.7017</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.69104</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.74779</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3686</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14448</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19678</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.09451000000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.01991</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.08715000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.16961</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.21146</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16227</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.11193</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.24833</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20823</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.23406</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22513</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26255</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15425</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.09737999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21687</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19675</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25534</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48123</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39168</v>
       </c>
     </row>
   </sheetData>
